--- a/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>CNSL</t>
   </si>
@@ -656,416 +656,428 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45016</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44834</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44742</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44651</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44469</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44377</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44286</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44104</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43921</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43738</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42916</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42825</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>275200</v>
+      </c>
+      <c r="E8" s="3">
         <v>283700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>275200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>276100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>296000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>296600</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>298400</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>300300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>318500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>318600</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>645200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>324800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>326100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>327100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>325200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>325700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>331000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>333300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>333500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>338600</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>344800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>348100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>350200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>356000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>356400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>363300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>170000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>169900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>175900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>191500</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>120500</v>
+      </c>
+      <c r="E9" s="3">
         <v>132400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>127000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>131900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>133700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>141200</v>
-      </c>
-      <c r="I9" s="3">
-        <v>135900</v>
       </c>
       <c r="J9" s="3">
         <v>135900</v>
       </c>
       <c r="K9" s="3">
+        <v>135900</v>
+      </c>
+      <c r="L9" s="3">
         <v>137800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>142500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>289300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>144000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>138900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>144400</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>139500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>137800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>136200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>146600</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>143800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>148300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>154700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>152900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>151400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>152900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>155500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>148400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>71100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>71000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>76700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E10" s="3">
         <v>151300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>148200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>144200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>162300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>155400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>162500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>164400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>180700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>176100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>355900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>180800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>187200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>182700</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>185700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>187900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>194800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>186700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>189700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>190300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>190100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>195200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>198800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>203100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>200900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>214900</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>98900</v>
       </c>
       <c r="AD10" s="3">
         <v>98900</v>
       </c>
       <c r="AE10" s="3">
+        <v>98900</v>
+      </c>
+      <c r="AF10" s="3">
         <v>99200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1110,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1203,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,192 +1298,201 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>13800</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>77800</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
         <v>0</v>
       </c>
       <c r="H14" s="3">
+        <v>0</v>
+      </c>
+      <c r="I14" s="3">
         <v>5200</v>
       </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>126500</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>5700</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>17100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>12000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>26100</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
       <c r="Q14" s="3">
         <v>0</v>
       </c>
       <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>-200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>-3100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>3000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>27100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>1800</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1300</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>7800</v>
       </c>
-      <c r="AF14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E15" s="3">
         <v>79600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>79500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>77700</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>79600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>75700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>72500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>72400</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>75100</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>73800</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>151700</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>75600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>80800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>80200</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>81100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>82700</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>91600</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>93000</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>97300</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>99200</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>103900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>109100</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>111700</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>107900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>104800</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>104400</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>40500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>42200</v>
-      </c>
-      <c r="AE15" s="3">
-        <v>43200</v>
       </c>
       <c r="AF15" s="3">
         <v>43200</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1522,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>288300</v>
+      </c>
+      <c r="E17" s="3">
         <v>315500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>370200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>294200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>316700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>275800</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>283900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>408000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>284200</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>286100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>593900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>298400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>323600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>289700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>285400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>288100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>301200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>308700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>319000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>321900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>340100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>347300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>344800</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>346800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>349400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>371000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>149400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>150900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>165000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>168800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-13100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-31800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-95000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-18100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-20700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>14500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-107700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>34300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>32500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>51300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>37400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>39800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>29800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>24600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>14500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>4700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>9200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>20600</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>19000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10900</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,192 +1747,199 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-44900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-36100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-31500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-31100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-29300</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-27100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-26200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-28200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-32200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-168000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-83600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-12300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-18200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-21600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-17000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-33600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-23000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-25600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-27000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-25600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-24600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-20000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-24900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E21" s="3">
         <v>11700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-47000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>29600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>67400</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>59900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-61600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>81300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>74100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>34900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>18400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>71000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>99400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>99300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>103400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-5200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-2700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-13000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>88900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-26100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-26400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>92500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-14700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>29200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-5700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>36300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>131500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1928,17 +1967,17 @@
       <c r="K22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L22" s="3">
+      <c r="L22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M22" s="3">
         <v>10900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>21100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>10200</v>
-      </c>
-      <c r="O22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P22" s="3" t="s">
         <v>8</v>
@@ -1955,8 +1994,8 @@
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -1991,192 +2030,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E23" s="3">
         <v>-67900</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-126500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-49200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-50000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-8200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-12600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-133900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>6100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-10500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-137900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-67400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-9800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>18200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>20700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-3800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-11100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-10300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-20900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-23800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-14600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-15000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-34700</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-10700</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-18400</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-12200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-9200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-1000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-2000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-14800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-4400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-3000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-3800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3100</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-6100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-9000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-4000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-6300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2315,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-47300</v>
+      </c>
+      <c r="E26" s="3">
         <v>-57700</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-108100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-37000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-40800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-7300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-10600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-119100</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>7400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-13100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-133400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-62100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-6800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>13900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>15600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-5800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-7300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7200</v>
-      </c>
-      <c r="W26" s="3">
-        <v>-14800</v>
       </c>
       <c r="X26" s="3">
         <v>-14800</v>
       </c>
       <c r="Y26" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="Z26" s="3">
         <v>-10600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-12900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-28400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE26" s="3">
-        <v>0</v>
-      </c>
       <c r="AF26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="E27" s="3">
         <v>-69200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-119000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-47700</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-51300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-17700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-20600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-128800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>4900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-13300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-133700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-62100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-8800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>13500</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>15300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-6000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-7400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-14900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-15100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-13200</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2600,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2558,37 +2618,37 @@
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>5800</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>299900</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>9100</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>3500</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>7500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>8600</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>16300</v>
       </c>
-      <c r="N29" s="3" t="s">
+      <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
@@ -2605,23 +2665,23 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>800</v>
       </c>
-      <c r="X29" s="3">
+      <c r="Y29" s="3">
         <v>4400</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>112900</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2635,8 +2695,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2790,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,192 +2885,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E32" s="3">
         <v>36100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>31500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>31100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>29300</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>27100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>26200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>28200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>32200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>168000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>83600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>12300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>18200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>21600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>17000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>33600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>23000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>25600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>27000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>25600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>24600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>20000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>24600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>22100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>27000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>24600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>24900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>10100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="E33" s="3">
         <v>-69200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-119000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-47700</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-45500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>282300</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-11500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-125300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>12400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-4700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-117500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-62100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-8800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>13500</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>15300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-6000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-7400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-14100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>99700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3170,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="E35" s="3">
         <v>-69200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-119000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-47700</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-45500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>282300</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-11500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-125300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>12400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-4700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-117500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-62100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-8800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>13500</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>15300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-6000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-7400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-14100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>99700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45016</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44834</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44742</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44651</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44469</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44377</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44286</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44104</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43921</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43738</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42916</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42825</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3402,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,135 +3437,139 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4800</v>
+      </c>
+      <c r="E41" s="3">
         <v>89600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>202600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>247900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>325900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>462000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>18000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>74200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>99600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>98700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>199300</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>325100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>155600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>99700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>45900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>14100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>12400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>10600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>11100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>15700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>23300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>26600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>27100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
       </c>
       <c r="F42" s="3">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>88000</v>
       </c>
       <c r="H42" s="3">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>25000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>85800</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>110800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>155000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>90000</v>
-      </c>
-      <c r="N42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O42" s="3" t="s">
         <v>8</v>
@@ -3497,8 +3586,8 @@
       <c r="S42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
+      <c r="T42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U42" s="3">
         <v>0</v>
@@ -3536,100 +3625,106 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E43" s="3">
         <v>111000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>107600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>110100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>121300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>116000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>120200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>121300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>134500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>135000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>130000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>126700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>138700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>124300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>120900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>126500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>122700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>137200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>144900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>143400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>144200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>155500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>134600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>156000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>143400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>144300</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>76400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>73800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>77800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>77600</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3720,468 +3815,486 @@
       <c r="AF44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>127300</v>
+      </c>
+      <c r="E45" s="3">
         <v>121700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>129100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>65600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>63000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>156600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>152900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>155700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>82900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>82500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>51400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>48600</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>46400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>42500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>41200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>45200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>41800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>42100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>45200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>44300</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>40600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>64400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>61700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>54600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>55300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>25900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>29000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>28300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>256200</v>
+      </c>
+      <c r="E46" s="3">
         <v>322300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>439400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>511600</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>598100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>734600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>316100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>437000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>427800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>471200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>470800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>500500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>340700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>266400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>207900</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>185800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>176900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>185400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>200600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>195900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>198100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>199900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>209600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>228900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>213700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>222900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>118100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>129500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>133200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>129100</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E47" s="3">
         <v>9000</v>
-      </c>
-      <c r="E47" s="3">
-        <v>9100</v>
       </c>
       <c r="F47" s="3">
         <v>9100</v>
       </c>
       <c r="G47" s="3">
-        <v>10300</v>
+        <v>9100</v>
       </c>
       <c r="H47" s="3">
         <v>10300</v>
       </c>
       <c r="I47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="J47" s="3">
         <v>107500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>109000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>109600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>109300</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>110800</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>111700</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>111600</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>112500</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>113200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>112700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>112400</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>112200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>112000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>110900</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>110700</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>110100</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>107100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>108900</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>108300</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>106500</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>106000</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>106200</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2449000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2429200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2390100</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2330500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2234100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2175600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2101100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>1983800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2019400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1905700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1831200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1772700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1760200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1782200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1793300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1806900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1862100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1888600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1899900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1926300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1927100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1955800</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1986300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>2019400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2037600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2058400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>1042800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1047800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1055200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1065500</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>843800</v>
+      </c>
+      <c r="E49" s="3">
         <v>849200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>855000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>977100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>983200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>990900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>998600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1006400</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1097700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1108200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1139600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1149400</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1159200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1171900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1184600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1197200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1209900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1226300</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1243000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1259100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1275700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1292900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1310200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1325500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1344800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1360800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>784100</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>785400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>788500</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>795800</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4385,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4480,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>70600</v>
+      </c>
+      <c r="E52" s="3">
         <v>76200</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>65900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>63500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>61300</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>57600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>62300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>59300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>58100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>134600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>135700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>140500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>135600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>51700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>49300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>51900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>28700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>30600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>23400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>36700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>30600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>28000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>14200</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>10900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>9600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4670,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3628400</v>
+      </c>
+      <c r="E54" s="3">
         <v>3686000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3759400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3891900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3887100</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3969000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3585700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3595400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3712700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3729000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3686800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3673800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3507300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3383800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3347600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3355100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3390300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3443300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3485700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3524000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3535300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3596000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3646800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3708900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3719100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3761200</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>2061100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2078200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2092800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2104200</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4802,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,560 +4837,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>60100</v>
+      </c>
+      <c r="E57" s="3">
         <v>44400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>50300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>33100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>30400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>58800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>39800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>41000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>47900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43500</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>27200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>25300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>22400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>16700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>19900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>30900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>32200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>44700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>26000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>32500</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>15700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>23100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>21000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>24100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>14200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>10100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>6400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>18400</v>
+      </c>
+      <c r="E58" s="3">
         <v>15500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>16800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16400</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>12800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>10300</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>9500</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>8400</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>6900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>17600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>23800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>24900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>25700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>27300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>29000</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>29300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>30500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>31800</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>32600</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>31600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>29700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>28800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>17800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>15800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>14900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>238700</v>
+      </c>
+      <c r="E59" s="3">
         <v>258200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>248900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>248400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>221000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>262800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>228200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>254200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>236600</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>266200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>225500</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>242500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>227600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>216900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>183200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>192100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>186100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>198300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>190400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>229700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>220600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>231000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>213300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>221000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>202100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>209900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>136800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>138100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>128400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>122200</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>317200</v>
+      </c>
+      <c r="E60" s="3">
         <v>318100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>316000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>318700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>266900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>303500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>296500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>302400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>285500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>321100</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>275400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>274700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>270500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>263100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>224800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>237700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>244300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>258400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>264100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>285000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>283600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>278500</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>268900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>273600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>255900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>252900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>164700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>160400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>150100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2134900</v>
+      </c>
+      <c r="E61" s="3">
         <v>2129100</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2135300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2136800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2129500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2126000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2124000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2120900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2118900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2115300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2113300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2105800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1932700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2193800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2198000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2209700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2250700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2285200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2309100</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2308100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2303600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2302800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2308800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2317400</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2311500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2311200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1376200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1375300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1376800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1377500</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>396900</v>
+      </c>
+      <c r="E62" s="3">
         <v>393400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>408800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>431200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>445300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>506700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>430900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>443300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>471900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>891000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1014600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>960800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>914900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>535300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>552700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>554100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>548100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>540000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>553300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>554800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>532400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>526200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>554900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>573800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>577700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>695400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>386900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>385800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>389700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>363500</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5500,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5595,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5690,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2857200</v>
+      </c>
+      <c r="E66" s="3">
         <v>2848700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2868100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2894500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2849300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2943700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2858800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2873800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2883400</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>3334500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3410300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3348000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3124800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>2998900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2982000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3007900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3049400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3089800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3132600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3153900</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3125500</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3113400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3138300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3170500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3150800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3265000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>1933300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1926800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1921800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1897900</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5822,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5915,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,38 +6010,41 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>372600</v>
+      </c>
+      <c r="E70" s="3">
         <v>361300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>350000</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>339300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>328700</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>318300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>308000</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>298200</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>288600</v>
       </c>
-      <c r="L70" s="3">
-        <v>0</v>
-      </c>
       <c r="M70" s="3">
         <v>0</v>
       </c>
@@ -5938,8 +6105,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6200,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-262400</v>
+      </c>
+      <c r="E72" s="3">
         <v>-215100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-157200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-49000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-11900</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>23300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-259000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-257300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-141600</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-156700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-152000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-96600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-34500</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-27600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-42100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-55800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-71200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-65200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-65500</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-58100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-50800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-36900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-21900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-11300</v>
       </c>
-      <c r="AA72" s="3" t="s">
+      <c r="AB72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-34900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-6400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE72" s="3">
-        <v>0</v>
-      </c>
       <c r="AF72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6390,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6485,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6580,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>398700</v>
+      </c>
+      <c r="E76" s="3">
         <v>476000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>541300</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>658200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>709100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>707000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>418900</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>423500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>540700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>394400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>276500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>325800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>382500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>385000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>365700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>347200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>340900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>353500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>353100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>370200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>409700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>482600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>508500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>538300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>568300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>496200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>127800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>151500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>171000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>206300</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6770,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45016</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44834</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44742</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44651</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44469</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44377</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44286</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44104</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43921</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43738</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42916</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42825</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-58600</v>
+      </c>
+      <c r="E81" s="3">
         <v>-69200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-119000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-47700</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-45500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>282300</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-11500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-125300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>12400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-4700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-117500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-62100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-8800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>13500</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>15300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-6000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-7400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-14100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-10700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10900</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-11500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>99700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-28600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,58 +7002,59 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>78300</v>
+      </c>
+      <c r="E83" s="3">
         <v>79600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>79500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>77700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>75700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>72500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>72400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75100</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>73800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>151700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>75600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>80800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>80200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>81100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>82700</v>
-      </c>
-      <c r="S83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T83" s="3" t="s">
         <v>8</v>
@@ -6873,8 +7071,8 @@
       <c r="X83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y83" s="3">
-        <v>0</v>
+      <c r="Y83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z83" s="3">
         <v>0</v>
@@ -6897,8 +7095,11 @@
       <c r="AF83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7190,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7285,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7380,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7475,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7570,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12000</v>
+      </c>
+      <c r="E89" s="3">
         <v>35300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>55100</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>5600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>76600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>59900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>81600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>22900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>110100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>185800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>98500</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>67600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>115600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>96700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>85000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>90500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>85400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>88300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>75000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>93300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>69700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>103500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>90800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>84800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>31700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>41800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>51700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>44600</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7702,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-90800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-143300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-150000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-130800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-123000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-164000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-176400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-156500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-140900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-144300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-195200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-76000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-65300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-53800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-42400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-47900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-64600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-66400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-53400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-58100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-61900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-64000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61200</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-29000</v>
       </c>
       <c r="AD91" s="3">
         <v>-29000</v>
       </c>
       <c r="AE91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-31900</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7890,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7985,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-91000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-144000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-53500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-128900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-135300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>370000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-113900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-104600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-93300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-209300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-283900</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-74700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-65300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-55100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-50000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-39800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-47700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-64400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-53500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-52200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-57600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-40700</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-62700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-60400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-61300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-923400</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-29000</v>
       </c>
       <c r="AD94" s="3">
         <v>-29000</v>
       </c>
       <c r="AE94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-21700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,8 +8117,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7942,10 +8175,10 @@
         <v>0</v>
       </c>
       <c r="U96" s="3">
+        <v>0</v>
+      </c>
+      <c r="V96" s="3">
         <v>-27900</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-27600</v>
       </c>
       <c r="W96" s="3">
         <v>-27600</v>
@@ -7957,7 +8190,7 @@
         <v>-27600</v>
       </c>
       <c r="Z96" s="3">
-        <v>-27400</v>
+        <v>-27600</v>
       </c>
       <c r="AA96" s="3">
         <v>-27400</v>
@@ -7966,10 +8199,10 @@
         <v>-27400</v>
       </c>
       <c r="AC96" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-19700</v>
-      </c>
-      <c r="AD96" s="3">
-        <v>-19600</v>
       </c>
       <c r="AE96" s="3">
         <v>-19600</v>
@@ -7977,8 +8210,11 @@
       <c r="AF96" s="3">
         <v>-19600</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-19600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8305,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8400,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,100 +8495,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-5900</v>
+      </c>
+      <c r="E100" s="3">
         <v>-4200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-6500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-2600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>71400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>141800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>145800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>53500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-15000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-43500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-36500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-25200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-31100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25700</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-29900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-35800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-41300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-34900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-31100</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>899200</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-23600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-29300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8437,96 +8685,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-84900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-113000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-45300</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-78000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-136200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>444000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-56200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-25500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-100600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>43800</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>169600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>55800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>53800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>31700</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>6200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-4300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-2900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>5800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-7700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>7500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-10800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>CNSL</t>
   </si>
@@ -656,428 +656,441 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45016</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44834</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44742</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44651</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44469</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44377</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44286</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44104</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44012</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43921</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43738</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42916</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42825</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>274700</v>
+      </c>
+      <c r="E8" s="3">
         <v>275200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>283700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>275200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>276100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>296000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>296600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>298400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>300300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>318500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>318600</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>645200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>324800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>326100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>327100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>325200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>325700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>331000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>333300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>333500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>338600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>344800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>348100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>350200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>356000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>356400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>363300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>170000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>169900</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>175900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>191500</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>113500</v>
+      </c>
+      <c r="E9" s="3">
         <v>120500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>132400</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>127000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>131900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>133700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>141200</v>
-      </c>
-      <c r="J9" s="3">
-        <v>135900</v>
       </c>
       <c r="K9" s="3">
         <v>135900</v>
       </c>
       <c r="L9" s="3">
+        <v>135900</v>
+      </c>
+      <c r="M9" s="3">
         <v>137800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>142500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>289300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>144000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>138900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>144400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>139500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>137800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>136200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>146600</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>143800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>148300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>154700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>152900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>151400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>152900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>155500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>148400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>71100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>71000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>76700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>161200</v>
+      </c>
+      <c r="E10" s="3">
         <v>154700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>151300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>148200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>144200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>162300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>155400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>162500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>164400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>180700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>176100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>355900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>180800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>187200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>182700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>185700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>187900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>194800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>186700</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>189700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>190300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>190100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>195200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>198800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>203100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>200900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>214900</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>98900</v>
       </c>
       <c r="AE10" s="3">
         <v>98900</v>
       </c>
       <c r="AF10" s="3">
+        <v>98900</v>
+      </c>
+      <c r="AG10" s="3">
         <v>99200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1111,8 +1124,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1206,8 +1220,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1301,198 +1318,207 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>2900</v>
+      </c>
+      <c r="E14" s="3">
         <v>13800</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>77800</v>
       </c>
-      <c r="G14" s="3">
-        <v>0</v>
-      </c>
       <c r="H14" s="3">
         <v>0</v>
       </c>
       <c r="I14" s="3">
+        <v>0</v>
+      </c>
+      <c r="J14" s="3">
         <v>5200</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>126500</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>5700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>17100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>12000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>26100</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
-      </c>
       <c r="R14" s="3">
         <v>0</v>
       </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>-3100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-1100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-200</v>
       </c>
-      <c r="W14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>200</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>100</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>3000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>27100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>1800</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1300</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>7800</v>
       </c>
-      <c r="AG14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E15" s="3">
         <v>78300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>79600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>79500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>77700</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>79600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>75700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>72500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>72400</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>75100</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>73800</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>151700</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>75600</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>80800</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>80200</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>81100</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>82700</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>91600</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>93000</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>97300</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>99200</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>103900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>109100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>111700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>107900</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>104800</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>104400</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>40500</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>42200</v>
-      </c>
-      <c r="AF15" s="3">
-        <v>43200</v>
       </c>
       <c r="AG15" s="3">
         <v>43200</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1523,198 +1549,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>281000</v>
+      </c>
+      <c r="E17" s="3">
         <v>288300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>315500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>370200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>294200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>316700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>275800</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>283900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>408000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>284200</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>286100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>593900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>298400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>323600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>289700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>285400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>288100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>301200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>308700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>319000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>321900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>340100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>347300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>344800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>346800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>349400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>371000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>149400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>150900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>165000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>168800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-6300</v>
+      </c>
+      <c r="E18" s="3">
         <v>-13100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-31800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-95000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-18100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-20700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>20800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>14500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-107700</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>34300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>51300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>26400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>37400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>39800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>37600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>29800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>24600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>14500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>4700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>9200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>7000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>20600</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>19000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10900</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1748,198 +1781,205 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-40900</v>
+      </c>
+      <c r="E20" s="3">
         <v>-44900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-36100</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-31500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-31100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-29300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-29100</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-27100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-26200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-28200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-32200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-168000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-83600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-12300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-18200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-21600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-17000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-33600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-23000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-25600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-27000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-25600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-24600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-24900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>33500</v>
+      </c>
+      <c r="E21" s="3">
         <v>20300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-47000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>28500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>29600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>67400</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>59900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-61600</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>81300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>74100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>34900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>18400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>71000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>99400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>99300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>103400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>-5200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-2700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-13000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>88900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-26100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-26400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>92500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-14700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>29200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>36300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>131500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1970,17 +2010,17 @@
       <c r="L22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M22" s="3">
+      <c r="M22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N22" s="3">
         <v>10900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>21100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>10200</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q22" s="3" t="s">
         <v>8</v>
@@ -1997,8 +2037,8 @@
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2033,198 +2073,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E23" s="3">
         <v>-58000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-67900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-126500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-49200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-50000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-8200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-12600</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-133900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>6100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-10500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-137900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-67400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-9800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>18200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>20700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-3800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-11100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-10300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-20900</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-23800</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-15000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-34700</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>700</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-11800</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10700</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-10200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-18400</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-12200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-9200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-1000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-2000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-14800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-1300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-4400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-3000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-3800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3100</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-6100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-9000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-6300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2318,198 +2367,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-35400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-47300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-57700</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-108100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-37000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-40800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-7300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-119100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>7400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-13100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-133400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-62100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-6800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>13900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>15600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-5800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-7300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7200</v>
-      </c>
-      <c r="X26" s="3">
-        <v>-14800</v>
       </c>
       <c r="Y26" s="3">
         <v>-14800</v>
       </c>
       <c r="Z26" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="AA26" s="3">
         <v>-10600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-12900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-28400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF26" s="3">
-        <v>0</v>
-      </c>
       <c r="AG26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E27" s="3">
         <v>-58600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-69200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-119000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-47700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-51300</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-17700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-20600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-128800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>4900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-13300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-133700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-62100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>13500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>15300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-6000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-7400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-14900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-15100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-13200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-28600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2603,13 +2661,16 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
-        <v>0</v>
+      <c r="D29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E29" s="3">
         <v>0</v>
@@ -2621,37 +2682,37 @@
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>5800</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>299900</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>9100</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>3500</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>7500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>8600</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>16300</v>
       </c>
-      <c r="O29" s="3" t="s">
+      <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
@@ -2668,23 +2729,23 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>800</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>4400</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>112900</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2698,8 +2759,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2793,8 +2857,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2888,198 +2955,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>40900</v>
+      </c>
+      <c r="E32" s="3">
         <v>44900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>36100</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>31500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>31100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>29300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>29100</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>27100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>26200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>28200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>32200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>168000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>83600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>12300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>18200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>21600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>17000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>33600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>23000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>25600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>27000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>25600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>24600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>20000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>24600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>22100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>27000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>24600</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>24900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>10100</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E33" s="3">
         <v>-58600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-69200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-119000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-47700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-45500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>282300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-11500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-125300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>12400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-4700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-117500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-62100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>13500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>15300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-6000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-7400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>99700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-28600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3173,203 +3249,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E35" s="3">
         <v>-58600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-69200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-119000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-47700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-45500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>282300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-11500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-125300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>12400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-4700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-117500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-62100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>13500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>15300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-6000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-7400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>99700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-28600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45016</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44834</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44742</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44651</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44469</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44377</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44286</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44104</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44012</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43921</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43738</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42916</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42825</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3403,8 +3488,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3438,141 +3524,145 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E41" s="3">
         <v>4800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>89600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>202600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>247900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>325900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>462000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>18000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>74200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>99600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>98700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>199300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>325100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>155600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>99700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>45900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>14100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>12400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>10500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>10600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>11100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>15700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>23300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>26600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>27100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
       </c>
       <c r="G42" s="3">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="H42" s="3">
         <v>88000</v>
       </c>
       <c r="I42" s="3">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>25000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>85800</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>110800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>155000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>90000</v>
-      </c>
-      <c r="O42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P42" s="3" t="s">
         <v>8</v>
@@ -3589,8 +3679,8 @@
       <c r="T42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
+      <c r="U42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V42" s="3">
         <v>0</v>
@@ -3628,103 +3718,109 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>112400</v>
+      </c>
+      <c r="E43" s="3">
         <v>124100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>111000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>107600</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>110100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>121300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>116000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>120200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>121300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>134500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>135000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>130000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>126700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>138700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>124300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>120900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>126500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>122700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>137200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>144900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>143400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>144200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>155500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>134600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>156000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>143400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>144300</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>76400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>73800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>77800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>77600</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3818,483 +3914,501 @@
       <c r="AG44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>133700</v>
+      </c>
+      <c r="E45" s="3">
         <v>127300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>121700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>129100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>65600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>63000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>156600</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>152900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>155700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>82900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>82500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>51400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>48600</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>46400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>42500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>41200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>45200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>41800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>42100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>45200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>45800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>44300</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>40600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>64400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>61700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>54600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>55300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>25900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>29000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>28300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>253500</v>
+      </c>
+      <c r="E46" s="3">
         <v>256200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>322300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>439400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>511600</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>598100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>734600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>316100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>437000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>427800</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>471200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>470800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>500500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>340700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>266400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>207900</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>185800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>176900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>185400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>200600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>195900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>198100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>199900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>209600</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>228900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>213700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>222900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>118100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>129500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>133200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>129100</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>8600</v>
+      </c>
+      <c r="E47" s="3">
         <v>8900</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>9000</v>
-      </c>
-      <c r="F47" s="3">
-        <v>9100</v>
       </c>
       <c r="G47" s="3">
         <v>9100</v>
       </c>
       <c r="H47" s="3">
-        <v>10300</v>
+        <v>9100</v>
       </c>
       <c r="I47" s="3">
         <v>10300</v>
       </c>
       <c r="J47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="K47" s="3">
         <v>107500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>109000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>109600</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109300</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>109500</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>110800</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>111700</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>111600</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>112500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>113200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>112700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>112400</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>112200</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>112000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>110900</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>110700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>110100</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>107100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>108900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>108300</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>106500</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>106000</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>106200</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2461000</v>
+      </c>
+      <c r="E48" s="3">
         <v>2449000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2429200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2390100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2330500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2234100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2175600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2101100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1983800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2019400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1905700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1831200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1772700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1760200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1782200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1793300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1806900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1862100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1888600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1899900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1926300</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1927100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1955800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>2019400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2037600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2058400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>1042800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1047800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1055200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1065500</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>839700</v>
+      </c>
+      <c r="E49" s="3">
         <v>843800</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>849200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>855000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>977100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>983200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>990900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>998600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1006400</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1097700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1108200</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1139600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1149400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1159200</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1171900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1184600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1197200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1209900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1226300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1243000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1259100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1275700</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1292900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1310200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1325500</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1344800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1360800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>784100</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>785400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>788500</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>795800</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4388,8 +4502,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4483,103 +4600,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>79400</v>
+      </c>
+      <c r="E52" s="3">
         <v>70600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>76200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>65900</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>63500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>61300</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>57600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>62300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>59300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>58100</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>134600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>135700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>140500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>135600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>51700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>49300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>51900</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>28700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>30600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>30700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>23400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>36700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>30600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>28000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>14200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>10900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>9600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4673,103 +4796,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3642200</v>
+      </c>
+      <c r="E54" s="3">
         <v>3628400</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3686000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3759400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3891900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3887100</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3969000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3585700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3595400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3712700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3729000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3686800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3673800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3507300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3383800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3347600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3355100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3390300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3443300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3485700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3524000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3535300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3596000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3646800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3708900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3719100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3761200</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>2061100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2078200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2092800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2104200</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4803,8 +4932,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4838,578 +4968,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>20500</v>
+      </c>
+      <c r="E57" s="3">
         <v>60100</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>44400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>50300</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>53900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>33100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>30400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>58800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>39800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>41000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>47900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43500</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>27200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>25300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>22400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>16700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>19900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>30900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>32200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>44700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>32500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>15700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>23100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>21000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>24100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>14200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>10100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>6400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>19200</v>
+      </c>
+      <c r="E58" s="3">
         <v>18400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>15500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>16800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16400</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>12800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>10300</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>9500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>8400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>6900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>5000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>17600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>23800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>24900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>25700</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>27300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>29000</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>29300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>30500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>31800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>32600</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>31600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>29700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>28800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>17800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>15800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>14900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>232700</v>
+      </c>
+      <c r="E59" s="3">
         <v>238700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>258200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>248900</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>248400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>221000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>262800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>228200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>254200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>236600</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>266200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>225500</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>242500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>227600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>216900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>183200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>192100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>186100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>198300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>190400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>229700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>220600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>231000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>213300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>221000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>202100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>209900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>136800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>138100</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>128400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>122200</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>272400</v>
+      </c>
+      <c r="E60" s="3">
         <v>317200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>318100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>316000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>318700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>266900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>303500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>296500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>302400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>285500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>321100</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>275400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>274700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>270500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>263100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>224800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>237700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>244300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>258400</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>264100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>285000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>283600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>278500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>268900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>273600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>255900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>252900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>164700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>160400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>150100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2234700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2134900</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2129100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2135300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2136800</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2129500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2126000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2124000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2120900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2118900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2115300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2113300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2105800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1932700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2193800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2198000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2209700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2250700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2285200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2309100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2308100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2303600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2302800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2308800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2317400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2311500</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2311200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1376200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1375300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1376800</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1377500</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>383800</v>
+      </c>
+      <c r="E62" s="3">
         <v>396900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>393400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>408800</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>431200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>445300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>506700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>430900</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>443300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>471900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>891000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1014600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>960800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>914900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>535300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>552700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>554100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>548100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>540000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>553300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>554800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>532400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>526200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>554900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>573800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>577700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>695400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>386900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>385800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>389700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>363500</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5503,8 +5652,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5598,8 +5750,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5693,103 +5848,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2899100</v>
+      </c>
+      <c r="E66" s="3">
         <v>2857200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2848700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2868100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2894500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2849300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2943700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2858800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2873800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2883400</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>3334500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3410300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3348000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3124800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>2998900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2982000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>3007900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3049400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3089800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3132600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3153900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3125500</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3113400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3138300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3170500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3150800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3265000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>1933300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1926800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1921800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1897900</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5823,8 +5984,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5918,8 +6080,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6013,41 +6178,44 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>384300</v>
+      </c>
+      <c r="E70" s="3">
         <v>372600</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>361300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>350000</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>339300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>328700</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>318300</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>308000</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>298200</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>288600</v>
       </c>
-      <c r="M70" s="3">
-        <v>0</v>
-      </c>
       <c r="N70" s="3">
         <v>0</v>
       </c>
@@ -6108,8 +6276,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6203,103 +6374,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-297900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-262400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-215100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-157200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-49000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-11900</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>23300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-259000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-257300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-141600</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-156700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-152000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-96600</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-34500</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-27600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-42100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-55800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-71200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-65200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-65500</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-58100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-50800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-36900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-21900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-11300</v>
       </c>
-      <c r="AB72" s="3" t="s">
+      <c r="AC72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-34900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-6400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF72" s="3">
-        <v>0</v>
-      </c>
       <c r="AG72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6393,8 +6570,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6488,8 +6668,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6583,103 +6766,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>358900</v>
+      </c>
+      <c r="E76" s="3">
         <v>398700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>476000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>541300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>658200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>709100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>707000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>418900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>423500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>540700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>394400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>276500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>325800</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>382500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>385000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>365700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>347200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>340900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>353500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>353100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>370200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>409700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>482600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>508500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>538300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>568300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>496200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>127800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>151500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>171000</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>206300</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6773,203 +6962,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45016</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44834</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44742</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44651</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44469</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44377</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44286</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44104</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44012</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43921</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43738</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42916</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42825</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-47200</v>
+      </c>
+      <c r="E81" s="3">
         <v>-58600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-69200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-119000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-47700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-45500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>282300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-11500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-125300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>12400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-4700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-117500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-62100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>13500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>15300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-6000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-7400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-14100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-10700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-11500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>99700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-28600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7003,61 +7201,62 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>80600</v>
+      </c>
+      <c r="E83" s="3">
         <v>78300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>79600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>77700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>79600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>75700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>72500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>75100</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>73800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>151700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>75600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>80800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>80200</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>81100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>82700</v>
-      </c>
-      <c r="T83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U83" s="3" t="s">
         <v>8</v>
@@ -7074,8 +7273,8 @@
       <c r="Y83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z83" s="3">
-        <v>0</v>
+      <c r="Z83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA83" s="3">
         <v>0</v>
@@ -7098,8 +7297,11 @@
       <c r="AG83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7193,8 +7395,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7288,8 +7493,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7383,8 +7591,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7478,8 +7689,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7573,103 +7787,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E89" s="3">
         <v>12000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>35300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12200</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>55100</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>5600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>76600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>59900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>81600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>22900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>110100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>185800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>98500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>67600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>115600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>96700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>85000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>90500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>85400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>88300</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>75000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>93300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>69700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>103500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>90800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>84800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>31700</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>41800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>51700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>44600</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7703,103 +7923,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-98000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-90800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-143300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-150000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-130800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-123000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-164000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-176400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-156500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-140900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-144300</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-195200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-76000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-56000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-53800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-42400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-47900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-64600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-66400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-53400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-58100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-61900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-64000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-61200</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-29000</v>
       </c>
       <c r="AE91" s="3">
         <v>-29000</v>
       </c>
       <c r="AF91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-31900</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7893,8 +8117,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7988,103 +8215,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-97200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-91000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-144000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-53500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-128900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-135300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>370000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-113900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-104600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-93300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-209300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-283900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-74700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-65300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-55100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-50000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-39800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-47700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-64400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-53500</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-52200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-57600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-40700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-62700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-60400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-61300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-923400</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-29000</v>
       </c>
       <c r="AE94" s="3">
         <v>-29000</v>
       </c>
       <c r="AF94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-21700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8118,8 +8351,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8178,10 +8412,10 @@
         <v>0</v>
       </c>
       <c r="V96" s="3">
+        <v>0</v>
+      </c>
+      <c r="W96" s="3">
         <v>-27900</v>
-      </c>
-      <c r="W96" s="3">
-        <v>-27600</v>
       </c>
       <c r="X96" s="3">
         <v>-27600</v>
@@ -8193,7 +8427,7 @@
         <v>-27600</v>
       </c>
       <c r="AA96" s="3">
-        <v>-27400</v>
+        <v>-27600</v>
       </c>
       <c r="AB96" s="3">
         <v>-27400</v>
@@ -8202,10 +8436,10 @@
         <v>-27400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-19700</v>
-      </c>
-      <c r="AE96" s="3">
-        <v>-19600</v>
       </c>
       <c r="AF96" s="3">
         <v>-19600</v>
@@ -8213,8 +8447,11 @@
       <c r="AG96" s="3">
         <v>-19600</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>-19600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8308,8 +8545,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8403,8 +8643,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8498,103 +8741,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>94200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-5900</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-4200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-6500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-2600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>71400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>141800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>145800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>53500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-6700</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-15000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-43500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-36500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-25200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-31100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25700</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-29900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-35800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-41300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-34900</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-31100</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>899200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-23600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-23200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-29300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8688,99 +8937,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>2600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-84900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-113000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-45300</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-78000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-136200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>444000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-56200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-25500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-100600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>43800</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>169600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>55800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>53800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>31700</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>1700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>6200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-4300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3700</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-2900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>5800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-6800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-500</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-7700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>7500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-10800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
   <si>
     <t>CNSL</t>
   </si>
@@ -656,441 +656,454 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45016</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44834</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44742</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44651</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44469</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44377</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44286</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44104</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44012</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43921</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43738</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42916</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42825</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>268700</v>
+      </c>
+      <c r="E8" s="3">
         <v>274700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>275200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>283700</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>275200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>276100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>296000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>296600</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>298400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>300300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>318500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>318600</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>645200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>324800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>326100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>327100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>325200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>325700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>331000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>333300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>333500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>338600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>344800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>348100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>350200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>356000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>356400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>363300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>170000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>169900</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>175900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>191500</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>114000</v>
+      </c>
+      <c r="E9" s="3">
         <v>113500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>120500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>132400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>127000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>131900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>133700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>141200</v>
-      </c>
-      <c r="K9" s="3">
-        <v>135900</v>
       </c>
       <c r="L9" s="3">
         <v>135900</v>
       </c>
       <c r="M9" s="3">
+        <v>135900</v>
+      </c>
+      <c r="N9" s="3">
         <v>137800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>142500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>289300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>144000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>138900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>144400</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>139500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>137800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>136200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>146600</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>143800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>148300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>154700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>152900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>151400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>152900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>155500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>148400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>71100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>71000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>76700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>154700</v>
+      </c>
+      <c r="E10" s="3">
         <v>161200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>154700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>151300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>148200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>144200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>162300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>155400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>162500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>164400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>180700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>176100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>355900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>180800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>187200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>182700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>185700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>187900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>194800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>186700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>189700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>190300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>190100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>195200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>198800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>203100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>200900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>214900</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>98900</v>
       </c>
       <c r="AF10" s="3">
         <v>98900</v>
       </c>
       <c r="AG10" s="3">
+        <v>98900</v>
+      </c>
+      <c r="AH10" s="3">
         <v>99200</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1125,8 +1138,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1223,8 +1237,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1321,204 +1338,213 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E14" s="3">
         <v>2900</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>13800</v>
       </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
       <c r="G14" s="3">
+        <v>0</v>
+      </c>
+      <c r="H14" s="3">
         <v>77800</v>
       </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
       <c r="I14" s="3">
         <v>0</v>
       </c>
       <c r="J14" s="3">
+        <v>0</v>
+      </c>
+      <c r="K14" s="3">
         <v>5200</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>126500</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
-      </c>
       <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>5700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>17100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>12000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26100</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
         <v>0</v>
       </c>
       <c r="T14" s="3">
+        <v>0</v>
+      </c>
+      <c r="U14" s="3">
         <v>-200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-3100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-1100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-200</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>3000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>27100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>1800</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1300</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>7800</v>
       </c>
-      <c r="AH14" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E15" s="3">
         <v>80600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>78300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>79600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>79500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>77700</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>79600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>75700</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>72500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>72400</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>75100</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>73800</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>151700</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>75600</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>80800</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>80200</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>81100</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>82700</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>91600</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>93000</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>97300</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>99200</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>103900</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>109100</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>111700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>107900</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>104800</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>104400</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>40500</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>42200</v>
-      </c>
-      <c r="AG15" s="3">
-        <v>43200</v>
       </c>
       <c r="AH15" s="3">
         <v>43200</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>43200</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1550,204 +1576,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>290300</v>
+      </c>
+      <c r="E17" s="3">
         <v>281000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>288300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>315500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>370200</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>294200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>316700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>275800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>283900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>408000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>284200</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>286100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>593900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>298400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>323600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>289700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>285400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>288100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>301200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>308700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>319000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>321900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>340100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>347300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>344800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>346800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>349400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>371000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>149400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>150900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>165000</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>168800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>-21600</v>
+      </c>
+      <c r="E18" s="3">
         <v>-6300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-13100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-31800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-95000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-18100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-20700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-107700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>34300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>51300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>37400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>39800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>37600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>29800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>24600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>14500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>4700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>7000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>20600</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>19000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10900</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1782,204 +1815,211 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-43800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-40900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-44900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-36100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-31500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-31100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-29300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-29100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-27100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-26200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-28200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-32200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-168000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-83600</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-12300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-18200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-21600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-17000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-33600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-23000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-25600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-27000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-25600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-24900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>14400</v>
+      </c>
+      <c r="E21" s="3">
         <v>33500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>20300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>11700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-47000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>28500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>29600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>67400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>59900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-61600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>81300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>74100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>34900</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>18400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>71000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>99400</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>99300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>103400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-5200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-2700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-13000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>88900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>-26100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>92500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-14700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>29200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>36300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>131500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2013,17 +2053,17 @@
       <c r="M22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N22" s="3">
+      <c r="N22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O22" s="3">
         <v>10900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>21100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>10200</v>
-      </c>
-      <c r="Q22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R22" s="3" t="s">
         <v>8</v>
@@ -2040,8 +2080,8 @@
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2076,204 +2116,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-65400</v>
+      </c>
+      <c r="E23" s="3">
         <v>-47200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-58000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-67900</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-126500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-49200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-50000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-8200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-12600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-133900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>6100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-10500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-137900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-67400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-9800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>18200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>20700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-3800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-11100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-20900</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-23800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-15000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-34700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>700</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E24" s="3">
         <v>-11800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-10700</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-10200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-18400</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-12200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-9200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-1000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-2000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-14800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-1300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>2600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>-4400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-3000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>5000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-3800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-6100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-6300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2370,204 +2419,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-54800</v>
+      </c>
+      <c r="E26" s="3">
         <v>-35400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-47300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-57700</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-108100</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-37000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-40800</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-7300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-119100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>7400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-13100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-133400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-6800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>13900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>15600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-5800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-7300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7200</v>
-      </c>
-      <c r="Y26" s="3">
-        <v>-14800</v>
       </c>
       <c r="Z26" s="3">
         <v>-14800</v>
       </c>
       <c r="AA26" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="AB26" s="3">
         <v>-10600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-12900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-28400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG26" s="3">
-        <v>0</v>
-      </c>
       <c r="AH26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E27" s="3">
         <v>-47200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-58600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-69200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-119000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-47700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-51300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-17700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-20600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-128800</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>4900</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-13300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-133700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-8800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>13500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>15300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-6000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-7400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-14900</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-15100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-13200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2664,16 +2722,19 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2685,37 +2746,37 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>5800</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>299900</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>9100</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>3500</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>7500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>8600</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>16300</v>
       </c>
-      <c r="P29" s="3" t="s">
+      <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
@@ -2732,23 +2793,23 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>800</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="AA29" s="3">
         <v>4400</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>112900</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2762,8 +2823,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2860,8 +2924,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2958,204 +3025,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>43800</v>
+      </c>
+      <c r="E32" s="3">
         <v>40900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>44900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>36100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>31500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>31100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>29300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>29100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>27100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>26200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>28200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>32200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>168000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>83600</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>12300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>18200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>21600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>17000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>33600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>23000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>25600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>27000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>25600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>24600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>20000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>24600</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>22100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>27000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>24600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>24900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>10100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E33" s="3">
         <v>-47200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-58600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-69200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-119000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-47700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-45500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>282300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-11500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-125300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>12400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-4700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-117500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-8800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>13500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>15300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-6000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-7400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>99700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3252,209 +3328,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E35" s="3">
         <v>-47200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-58600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-69200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-119000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-47700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-45500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>282300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-11500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-125300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>12400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-4700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-117500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-8800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>13500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>15300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-6000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-7400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>99700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45016</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44834</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44742</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44651</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44469</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44377</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44286</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44104</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44012</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43921</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43738</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42916</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42825</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3489,8 +3574,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3525,106 +3611,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E41" s="3">
         <v>7400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>4800</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>89600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>202600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>247900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>325900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>462000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>18000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>74200</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>99600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>98700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>199300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>325100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>155600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>99700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>45900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>14100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>12400</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>6200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>10500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>3800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>10600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>11100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>15700</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>23300</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>15900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>26600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>27100</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3634,38 +3724,38 @@
       <c r="E42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
+      <c r="F42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
       <c r="H42" s="3">
-        <v>88000</v>
+        <v>0</v>
       </c>
       <c r="I42" s="3">
         <v>88000</v>
       </c>
       <c r="J42" s="3">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>25000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>85800</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>110800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>155000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>90000</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q42" s="3" t="s">
         <v>8</v>
@@ -3682,8 +3772,8 @@
       <c r="U42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V42" s="3">
-        <v>0</v>
+      <c r="V42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W42" s="3">
         <v>0</v>
@@ -3721,106 +3811,112 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>130800</v>
+      </c>
+      <c r="E43" s="3">
         <v>112400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>124100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>111000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>107600</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>110100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>121300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>116000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>120200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>121300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>134500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>135000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>130000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>126700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>138700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>124300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>120900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>126500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>122700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>137200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>144900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>143400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>144200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>155500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>134600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>156000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>143400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>144300</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>76400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>73800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>77800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>77600</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3917,204 +4013,213 @@
       <c r="AH44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>57300</v>
+      </c>
+      <c r="E45" s="3">
         <v>133700</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>127300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>121700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>129100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>65600</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>63000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>156600</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>152900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>155700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>82900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>82500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>51400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48600</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>46400</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>42500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>41200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>45200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>41800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>42100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>45200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>44300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>40600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>64400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>61700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>54600</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>55300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>25900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>29000</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>28300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>193500</v>
+      </c>
+      <c r="E46" s="3">
         <v>253500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>256200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>322300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>439400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>511600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>598100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>734600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>316100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>437000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>427800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>471200</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>470800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>500500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>340700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>266400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>207900</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>185800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>176900</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>185400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>200600</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>195900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>198100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>199900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>209600</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>228900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>213700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>222900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>118100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>129500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>133200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>129100</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4122,293 +4227,302 @@
         <v>8600</v>
       </c>
       <c r="E47" s="3">
+        <v>8600</v>
+      </c>
+      <c r="F47" s="3">
         <v>8900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>9000</v>
-      </c>
-      <c r="G47" s="3">
-        <v>9100</v>
       </c>
       <c r="H47" s="3">
         <v>9100</v>
       </c>
       <c r="I47" s="3">
-        <v>10300</v>
+        <v>9100</v>
       </c>
       <c r="J47" s="3">
         <v>10300</v>
       </c>
       <c r="K47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="L47" s="3">
         <v>107500</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>109000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109600</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>109300</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109500</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>110800</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>111700</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>111600</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>112500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>113200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>112700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>112400</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>112200</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>112000</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>110900</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>110700</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>110100</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>107100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>108900</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>108300</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>106500</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>106000</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>106200</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2494800</v>
+      </c>
+      <c r="E48" s="3">
         <v>2461000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2449000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>2429200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>2390100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2330500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2234100</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2175600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2101100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1983800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>2019400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>1905700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1831200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1772700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1760200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1782200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1793300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1806900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1862100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1888600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1899900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1926300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1927100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1955800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>2019400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2037600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2058400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>1042800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1047800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1055200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1065500</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>835700</v>
+      </c>
+      <c r="E49" s="3">
         <v>839700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>843800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>849200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>855000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>977100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>983200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>990900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>998600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1006400</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1097700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1108200</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1139600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1149400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1159200</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1171900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1184600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1197200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1209900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1226300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1243000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1259100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1275700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1292900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1310200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1325500</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1344800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1360800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>784100</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>785400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>788500</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>795800</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4505,8 +4619,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4603,106 +4720,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>77800</v>
+      </c>
+      <c r="E52" s="3">
         <v>79400</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>70600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>76200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>65900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>63500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>61300</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>57600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>62300</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>59300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>58100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>134600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>135700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>140500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>135600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>51700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>49300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>51900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>28700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>30600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>30100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>30700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>23400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>36700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>30600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>28000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>14200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>10900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>9600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4799,106 +4922,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3610300</v>
+      </c>
+      <c r="E54" s="3">
         <v>3642200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3628400</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3686000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3759400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3891900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3887100</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3969000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3585700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3595400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3712700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3729000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3686800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3673800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3507300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3383800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3347600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3355100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3390300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3443300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3485700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3524000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3535300</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3596000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3646800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3708900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3719100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3761200</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>2061100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2078200</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2092800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2104200</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4933,8 +5062,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4969,596 +5099,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E57" s="3">
         <v>20500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>60100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>44400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>50300</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>33100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>30400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>58800</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>39800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>41000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>47900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43500</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>27200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>25300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>22400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>16700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>19900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>30900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>44700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>26000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>15700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>23100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>21000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>24100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>14200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>10100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>6400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>20600</v>
+      </c>
+      <c r="E58" s="3">
         <v>19200</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>18400</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>15500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>16800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16400</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>12800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>10300</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>9500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>8400</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>5000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>17600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>23800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>24900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>25700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>27300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>29000</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>29300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>30500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>31800</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>32600</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>31600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>29700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>28800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>17800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>15800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>14900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>208400</v>
+      </c>
+      <c r="E59" s="3">
         <v>232700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>238700</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>258200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>248900</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>248400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>221000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>262800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>228200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>254200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>236600</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>266200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>225500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>242500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>227600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>216900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>183200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>192100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>186100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>198300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>190400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>229700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>220600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>231000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>213300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>221000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>202100</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>209900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>136800</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>138100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>128400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>122200</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>268800</v>
+      </c>
+      <c r="E60" s="3">
         <v>272400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>317200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>318100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>316000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>318700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>266900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>303500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>296500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>302400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>285500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>321100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>275400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>274700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>270500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>263100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>224800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>237700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>244300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>258400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>264100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>285000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>283600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>278500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>268900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>273600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>255900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>252900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>164700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>160400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>150100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2268700</v>
+      </c>
+      <c r="E61" s="3">
         <v>2234700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2134900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2129100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2135300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2136800</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2129500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2126000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2124000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2120900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2118900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2115300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2113300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2105800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1932700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2193800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2198000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2209700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2250700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2285200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2309100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2308100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2303600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2302800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2308800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2317400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2311500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2311200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1376200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1375300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1376800</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1377500</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>374800</v>
+      </c>
+      <c r="E62" s="3">
         <v>383800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>396900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>393400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>408800</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>431200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>445300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>506700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>430900</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>443300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>471900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>891000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1014600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>960800</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>914900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>535300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>552700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>554100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>548100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>540000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>553300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>554800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>532400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>526200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>554900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>573800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>577700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>695400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>386900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>385800</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>389700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>363500</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5655,8 +5804,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5753,8 +5905,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5851,106 +6006,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>2920600</v>
+      </c>
+      <c r="E66" s="3">
         <v>2899100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>2857200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>2848700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>2868100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>2894500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>2849300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>2943700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2858800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2873800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2883400</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>3334500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3410300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3348000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3124800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>2998900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2982000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>3007900</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3049400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3089800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3132600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3153900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3125500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3113400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3138300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3170500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3150800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3265000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>1933300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1926800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1921800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1897900</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5985,8 +6146,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6083,8 +6245,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6181,44 +6346,47 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>396000</v>
+      </c>
+      <c r="E70" s="3">
         <v>384300</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>372600</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>361300</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>350000</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>339300</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>328700</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>318300</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>308000</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>298200</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>288600</v>
       </c>
-      <c r="N70" s="3">
-        <v>0</v>
-      </c>
       <c r="O70" s="3">
         <v>0</v>
       </c>
@@ -6279,8 +6447,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6377,106 +6548,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-352800</v>
+      </c>
+      <c r="E72" s="3">
         <v>-297900</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-262400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-215100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-157200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-49000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-11900</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>23300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>-259000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-257300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-141600</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-156700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-152000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-96600</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-34500</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-27600</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-42100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-55800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-71200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-65200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-65500</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-58100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-50800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-36900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-21900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-11300</v>
       </c>
-      <c r="AC72" s="3" t="s">
+      <c r="AD72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>-34900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>-6400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG72" s="3">
-        <v>0</v>
-      </c>
       <c r="AH72" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI72" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6573,8 +6750,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6671,8 +6851,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6769,106 +6952,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>293700</v>
+      </c>
+      <c r="E76" s="3">
         <v>358900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>398700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>476000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>541300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>658200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>709100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>707000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>418900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>423500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>540700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>394400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>276500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>325800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>382500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>385000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>365700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>347200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>340900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>353500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>353100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>370200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>409700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>482600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>508500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>538300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>568300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>496200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>127800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>151500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>171000</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>206300</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6965,209 +7154,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45016</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44834</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44742</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44651</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44469</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44377</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44286</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44104</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44012</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43921</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43738</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42916</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42825</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>-66700</v>
+      </c>
+      <c r="E81" s="3">
         <v>-47200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-58600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-69200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-119000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-47700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-45500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>282300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-11500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-125300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>12400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-4700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-117500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-62100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-8800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>13500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>15300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-6000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-7400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-14100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-10700</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-11500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>99700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-28600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7202,64 +7400,65 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>79800</v>
+      </c>
+      <c r="E83" s="3">
         <v>80600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>78300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>79600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>79500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>77700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>79600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>75700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>72500</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>75100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>73800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>151700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>75600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>80800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>80200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>81100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>82700</v>
-      </c>
-      <c r="U83" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V83" s="3" t="s">
         <v>8</v>
@@ -7276,8 +7475,8 @@
       <c r="Z83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA83" s="3">
-        <v>0</v>
+      <c r="AA83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB83" s="3">
         <v>0</v>
@@ -7300,8 +7499,11 @@
       <c r="AH83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7398,8 +7600,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7496,8 +7701,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7594,8 +7802,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7692,8 +7903,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7790,106 +8004,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-8200</v>
+      </c>
+      <c r="E89" s="3">
         <v>5700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>12000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>35300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>12200</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>55100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>76600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>59900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>81600</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>22900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>110100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>185800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>98500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>67600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>115600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>96700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>85000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>90500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>85400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>88300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>75000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>93300</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>69700</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>103500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>90800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>84800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>31700</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>41800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>51700</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>44600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7924,106 +8144,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-85500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-98000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-90800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-143300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-150000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-130800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-123000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-164000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-176400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-156500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-140900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-144300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-195200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-76000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-65300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-56000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-53800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-42400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-47900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-64600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-66400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-53400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-58100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-64000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-61200</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-29000</v>
       </c>
       <c r="AF91" s="3">
         <v>-29000</v>
       </c>
       <c r="AG91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-31900</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8120,8 +8344,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8218,106 +8445,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-17900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-97200</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-91000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-144000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-53500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-128900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-135300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>370000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-113900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-104600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-93300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-209300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-283900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-74700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-65300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-55100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-50000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-39800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-47700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-64400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-53500</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-52200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-57600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-62700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-60400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-61300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-923400</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-29000</v>
       </c>
       <c r="AF94" s="3">
         <v>-29000</v>
       </c>
       <c r="AG94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-21700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8352,8 +8585,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8415,10 +8649,10 @@
         <v>0</v>
       </c>
       <c r="W96" s="3">
+        <v>0</v>
+      </c>
+      <c r="X96" s="3">
         <v>-27900</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-27600</v>
       </c>
       <c r="Y96" s="3">
         <v>-27600</v>
@@ -8430,7 +8664,7 @@
         <v>-27600</v>
       </c>
       <c r="AB96" s="3">
-        <v>-27400</v>
+        <v>-27600</v>
       </c>
       <c r="AC96" s="3">
         <v>-27400</v>
@@ -8439,10 +8673,10 @@
         <v>-27400</v>
       </c>
       <c r="AE96" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-19700</v>
-      </c>
-      <c r="AF96" s="3">
-        <v>-19600</v>
       </c>
       <c r="AG96" s="3">
         <v>-19600</v>
@@ -8450,8 +8684,11 @@
       <c r="AH96" s="3">
         <v>-19600</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>-19600</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8548,8 +8785,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8646,8 +8886,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8744,106 +8987,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E100" s="3">
         <v>94200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-5900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-4200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-6500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-2600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>71400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>141800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>145800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>53500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-6700</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-15000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-43500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-36500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-25200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-31100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-29900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-35800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-41300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-34900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-31100</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>899200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-23600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-23200</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-29300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8940,102 +9189,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E102" s="3">
         <v>2600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-84900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-113000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-45300</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-78000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-136200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>444000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-56200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-25500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-100600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>43800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>169600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>55800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>53800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>31700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>6200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-4300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>5800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-7700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>7500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-10800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>8800</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/CNSL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="92">
   <si>
     <t>CNSL</t>
   </si>
@@ -656,454 +656,467 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="7.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44834</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44742</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44651</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44469</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44377</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44286</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44104</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44012</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43921</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43738</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42916</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42825</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>271100</v>
+      </c>
+      <c r="E8" s="3">
         <v>268700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>274700</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>275200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>283700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>275200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>276100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>296000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>296600</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>298400</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>300300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>318500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>318600</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>645200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>324800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>326100</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>327100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>325200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>325700</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>331000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>333300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>333500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>338600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>344800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>348100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>350200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>356000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>356400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>363300</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>170000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>169900</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>175900</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>191500</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>113200</v>
+      </c>
+      <c r="E9" s="3">
         <v>114000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>113500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>120500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>132400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>127000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>131900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>133700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>141200</v>
-      </c>
-      <c r="L9" s="3">
-        <v>135900</v>
       </c>
       <c r="M9" s="3">
         <v>135900</v>
       </c>
       <c r="N9" s="3">
+        <v>135900</v>
+      </c>
+      <c r="O9" s="3">
         <v>137800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>142500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>289300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>144000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>138900</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>144400</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>139500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>137800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>136200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>146600</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>143800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>148300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>154700</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>152900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>151400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>152900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>155500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>148400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>71100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>71000</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>76700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>85600</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>157900</v>
+      </c>
+      <c r="E10" s="3">
         <v>154700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>161200</v>
       </c>
-      <c r="F10" s="3">
-        <v>154700</v>
-      </c>
       <c r="G10" s="3">
-        <v>151300</v>
+        <v>154600</v>
       </c>
       <c r="H10" s="3">
+        <v>151200</v>
+      </c>
+      <c r="I10" s="3">
         <v>148200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>144200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>162300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>155400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>162500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>164400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>180700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>176100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>355900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>180800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>187200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>182700</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>185700</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>187900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>194800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>186700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>189700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>190300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>190100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>195200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>198800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>203100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>200900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>214900</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>98900</v>
       </c>
       <c r="AG10" s="3">
         <v>98900</v>
       </c>
       <c r="AH10" s="3">
+        <v>98900</v>
+      </c>
+      <c r="AI10" s="3">
         <v>99200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>105900</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1139,8 +1152,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1240,8 +1254,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1341,210 +1358,219 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>600</v>
+      </c>
+      <c r="E14" s="3">
         <v>3200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2900</v>
       </c>
-      <c r="F14" s="3">
-        <v>13800</v>
-      </c>
       <c r="G14" s="3">
-        <v>0</v>
+        <v>10900</v>
       </c>
       <c r="H14" s="3">
-        <v>77800</v>
+        <v>7800</v>
       </c>
       <c r="I14" s="3">
-        <v>0</v>
+        <v>80100</v>
       </c>
       <c r="J14" s="3">
-        <v>0</v>
+        <v>3300</v>
       </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>5200</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
       <c r="M14" s="3">
+        <v>0</v>
+      </c>
+      <c r="N14" s="3">
         <v>126500</v>
       </c>
-      <c r="N14" s="3">
-        <v>0</v>
-      </c>
       <c r="O14" s="3">
+        <v>0</v>
+      </c>
+      <c r="P14" s="3">
         <v>5700</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>17100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>12000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26100</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>-200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>-3100</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>-1100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>-200</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>3000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>27100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>1800</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>1300</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>7800</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>76700</v>
+      </c>
+      <c r="E15" s="3">
         <v>79800</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>80600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>78300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>79600</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>79500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>77700</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>79600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>75700</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>72500</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>72400</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>75100</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>73800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>151700</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>75600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>80800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>80200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>81100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>82700</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>91600</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>93000</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>97300</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>99200</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>103900</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>109100</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>111700</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>107900</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>104800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>104400</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>40500</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>42200</v>
-      </c>
-      <c r="AH15" s="3">
-        <v>43200</v>
       </c>
       <c r="AI15" s="3">
         <v>43200</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>43200</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1577,210 +1603,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>290300</v>
+        <v>288600</v>
       </c>
       <c r="E17" s="3">
-        <v>281000</v>
+        <v>287100</v>
       </c>
       <c r="F17" s="3">
-        <v>288300</v>
+        <v>278100</v>
       </c>
       <c r="G17" s="3">
-        <v>315500</v>
+        <v>282200</v>
       </c>
       <c r="H17" s="3">
-        <v>370200</v>
+        <v>306600</v>
       </c>
       <c r="I17" s="3">
-        <v>294200</v>
+        <v>288900</v>
       </c>
       <c r="J17" s="3">
+        <v>289800</v>
+      </c>
+      <c r="K17" s="3">
         <v>316700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>275800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>283900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>408000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>284200</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>286100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>593900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>298400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>323600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>289700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>285400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>288100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>301200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>308700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>319000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>321900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>340100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>347300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>344800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>346800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>349400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>371000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>149400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>150900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>165000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>168800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-21600</v>
+        <v>-17500</v>
       </c>
       <c r="E18" s="3">
-        <v>-6300</v>
+        <v>-18400</v>
       </c>
       <c r="F18" s="3">
-        <v>-13100</v>
+        <v>-3400</v>
       </c>
       <c r="G18" s="3">
-        <v>-31800</v>
+        <v>-7000</v>
       </c>
       <c r="H18" s="3">
-        <v>-95000</v>
+        <v>-22900</v>
       </c>
       <c r="I18" s="3">
-        <v>-18100</v>
+        <v>-13800</v>
       </c>
       <c r="J18" s="3">
+        <v>-13600</v>
+      </c>
+      <c r="K18" s="3">
         <v>-20700</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-107700</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>34300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>32500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>51300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>2500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>37400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>39800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>37600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>29800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>24600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>14500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16700</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>4700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-7700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>20600</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>19000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10900</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>22700</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1816,233 +1849,240 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-43800</v>
+        <v>-100</v>
       </c>
       <c r="E20" s="3">
-        <v>-40900</v>
+        <v>-300</v>
       </c>
       <c r="F20" s="3">
-        <v>-44900</v>
+        <v>-1600</v>
       </c>
       <c r="G20" s="3">
-        <v>-36100</v>
+        <v>-1500</v>
       </c>
       <c r="H20" s="3">
-        <v>-31500</v>
+        <v>-2400</v>
       </c>
       <c r="I20" s="3">
-        <v>-31100</v>
+        <v>-4300</v>
       </c>
       <c r="J20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-29300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-29100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-27100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-26200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-28200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-32200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-168000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-83600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-12300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-18200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-21600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-17000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-33600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-23000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-25600</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-27000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-25600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-20000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-22100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-27000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-24600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-24900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-10100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-10600</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14400</v>
+        <v>59300</v>
       </c>
       <c r="E21" s="3">
-        <v>33500</v>
+        <v>61700</v>
       </c>
       <c r="F21" s="3">
-        <v>20300</v>
+        <v>78900</v>
       </c>
       <c r="G21" s="3">
-        <v>11700</v>
+        <v>72900</v>
       </c>
       <c r="H21" s="3">
-        <v>-47000</v>
+        <v>59100</v>
       </c>
       <c r="I21" s="3">
-        <v>28500</v>
+        <v>70000</v>
       </c>
       <c r="J21" s="3">
+        <v>65700</v>
+      </c>
+      <c r="K21" s="3">
         <v>29600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>67400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>59900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-61600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>81300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>74100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>34900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>18400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>71000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>99400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>99300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>103400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>-5200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>-2700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>-13000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>88900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-26100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-26400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-10700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>92500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>29200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>36300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>131500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>11800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>44900</v>
+      </c>
+      <c r="E22" s="3">
+        <v>44100</v>
+      </c>
+      <c r="F22" s="3">
+        <v>42500</v>
+      </c>
+      <c r="G22" s="3">
+        <v>41600</v>
+      </c>
+      <c r="H22" s="3">
+        <v>39600</v>
+      </c>
+      <c r="I22" s="3">
+        <v>36900</v>
+      </c>
+      <c r="J22" s="3">
+        <v>33900</v>
       </c>
       <c r="K22" s="3" t="s">
         <v>8</v>
@@ -2056,18 +2096,18 @@
       <c r="N22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O22" s="3">
+      <c r="O22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P22" s="3">
         <v>10900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>21100</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>10200</v>
       </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
@@ -2083,8 +2123,8 @@
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2119,210 +2159,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>-62900</v>
+      </c>
+      <c r="E23" s="3">
         <v>-65400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-47200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-58000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-67900</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-126500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-49200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-50000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-8200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-12600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-133900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>6100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-10500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-137900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-67400</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-9800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>19200</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>18200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>20700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-3800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>1600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>-11100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-10300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-20900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-23800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-14600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-15400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-15000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-34700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5900</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>700</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>12100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-13900</v>
+      </c>
+      <c r="E24" s="3">
         <v>-10600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-11800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-10700</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-10200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-18400</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-12200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>-9200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-1000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-2000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-14800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-1300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>-4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-3000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-3800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-6100</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-9000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-4200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-6300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-2200</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>5000</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2422,210 +2471,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>-49000</v>
+      </c>
+      <c r="E26" s="3">
         <v>-54800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-35400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-47300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-57700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-108100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-37000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-40800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-7300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-119100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>7400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-13100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-133400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-62100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-6800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>14600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>13900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>15600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-5800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>-7300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-7200</v>
-      </c>
-      <c r="Z26" s="3">
-        <v>-14800</v>
       </c>
       <c r="AA26" s="3">
         <v>-14800</v>
       </c>
       <c r="AB26" s="3">
+        <v>-14800</v>
+      </c>
+      <c r="AC26" s="3">
         <v>-10600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-11200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-12900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-28400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH26" s="3">
-        <v>0</v>
-      </c>
       <c r="AI26" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ26" s="3">
         <v>7100</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>-61400</v>
+      </c>
+      <c r="E27" s="3">
         <v>-66700</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-47200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-58600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-69200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-119000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-47700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-51300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-17700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-20600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-128800</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>4900</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-13300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-133700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-62100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-8800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>14100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>13500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>15300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-6000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-14900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-15100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-13200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-28600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2725,16 +2783,19 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
@@ -2749,37 +2810,37 @@
         <v>0</v>
       </c>
       <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>5800</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>299900</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>9100</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>3500</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>7500</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>8600</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>16300</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2796,24 +2857,24 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>800</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>4400</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>112900</v>
       </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2826,8 +2887,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2927,8 +2991,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3028,210 +3095,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>43800</v>
+        <v>100</v>
       </c>
       <c r="E32" s="3">
-        <v>40900</v>
+        <v>300</v>
       </c>
       <c r="F32" s="3">
-        <v>44900</v>
+        <v>1600</v>
       </c>
       <c r="G32" s="3">
-        <v>36100</v>
+        <v>1500</v>
       </c>
       <c r="H32" s="3">
-        <v>31500</v>
+        <v>2400</v>
       </c>
       <c r="I32" s="3">
-        <v>31100</v>
+        <v>4300</v>
       </c>
       <c r="J32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="K32" s="3">
         <v>29300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>29100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>27100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>26200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>28200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>32200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>168000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>83600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>12300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>18200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>21600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>17000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>33600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>23000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>25600</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>27000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>25600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>24600</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>20000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>24600</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>22100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>27000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>24600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>24900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>10100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>10600</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>-66700</v>
+        <v>-49100</v>
       </c>
       <c r="E33" s="3">
-        <v>-47200</v>
+        <v>-55000</v>
       </c>
       <c r="F33" s="3">
-        <v>-58600</v>
+        <v>-35500</v>
       </c>
       <c r="G33" s="3">
-        <v>-69200</v>
+        <v>-47300</v>
       </c>
       <c r="H33" s="3">
-        <v>-119000</v>
+        <v>-57900</v>
       </c>
       <c r="I33" s="3">
-        <v>-47700</v>
+        <v>-108300</v>
       </c>
       <c r="J33" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="K33" s="3">
         <v>-45500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>282300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-11500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-125300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>12400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-4700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-117500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-62100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-8800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>14100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>13500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>15300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-6000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>99700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-28600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3331,215 +3407,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>-66700</v>
+        <v>-49100</v>
       </c>
       <c r="E35" s="3">
-        <v>-47200</v>
+        <v>-55000</v>
       </c>
       <c r="F35" s="3">
-        <v>-58600</v>
+        <v>-35500</v>
       </c>
       <c r="G35" s="3">
-        <v>-69200</v>
+        <v>-47300</v>
       </c>
       <c r="H35" s="3">
-        <v>-119000</v>
+        <v>-57900</v>
       </c>
       <c r="I35" s="3">
-        <v>-47700</v>
+        <v>-108300</v>
       </c>
       <c r="J35" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="K35" s="3">
         <v>-45500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>282300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-11500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-125300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>12400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-4700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-117500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-62100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-8800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>14100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>13500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>15300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-6000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>99700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-28600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44834</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44742</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44651</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44469</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44377</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44286</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44104</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44012</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43921</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43738</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42916</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42825</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3575,8 +3660,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3612,120 +3698,124 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>44400</v>
+      </c>
+      <c r="E41" s="3">
         <v>5300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>4800</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>89600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>202600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>247900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>325900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>462000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>18000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>74200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>99600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>98700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>199300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>325100</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>155600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>99700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>45900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>14100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>12400</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>6200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>10500</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>6700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>10600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>11100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>15700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>23300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>15900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>26600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>27100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>33400</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
       </c>
       <c r="G42" s="3">
         <v>0</v>
@@ -3734,32 +3824,32 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J42" s="3">
+        <v>91600</v>
+      </c>
+      <c r="K42" s="3">
         <v>88000</v>
       </c>
-      <c r="J42" s="3">
-        <v>88000</v>
-      </c>
-      <c r="K42" s="3">
-        <v>0</v>
-      </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>25000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>85800</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>110800</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>155000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>90000</v>
       </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
       </c>
@@ -3775,8 +3865,8 @@
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3814,132 +3904,138 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>143200</v>
+      </c>
+      <c r="E43" s="3">
         <v>130800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>112400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>124100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>111000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>107600</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>110100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>121300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>116000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>120200</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>121300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>134500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>135000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>130000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>126700</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>138700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>124300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>120900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>126500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>122700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>137200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>144900</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>143400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>144200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>155500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>134600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>156000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>143400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>144300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>76400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>73800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>77800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>77600</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -4016,513 +4112,531 @@
       <c r="AI44" s="3">
         <v>0</v>
       </c>
+      <c r="AJ44" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>57300</v>
-      </c>
-      <c r="E45" s="3">
-        <v>133700</v>
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F45" s="3">
-        <v>127300</v>
+        <v>71000</v>
       </c>
       <c r="G45" s="3">
-        <v>121700</v>
+        <v>70500</v>
       </c>
       <c r="H45" s="3">
-        <v>129100</v>
+        <v>69800</v>
       </c>
       <c r="I45" s="3">
-        <v>65600</v>
-      </c>
-      <c r="J45" s="3">
+        <v>69000</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
         <v>63000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>156600</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>152900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>155700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>82900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>82500</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>51400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>48600</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>46400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>42500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>41200</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>45200</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>41800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>42100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>45200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>45800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>44300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>40600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>64400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>61700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>54600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>55300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>25900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>29000</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>28300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>18100</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>252100</v>
+      </c>
+      <c r="E46" s="3">
         <v>193500</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>253500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>256200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>322300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>439400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>511600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>598100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>734600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>316100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>437000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>427800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>471200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>470800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>500500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>340700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>266400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>207900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>185800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>176900</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>185400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>200600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>195900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>198100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>199900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>209600</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>228900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>213700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>222900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>118100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>129500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>133200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>129100</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>8600</v>
+        <v>5400</v>
       </c>
       <c r="E47" s="3">
-        <v>8600</v>
+        <v>10800</v>
       </c>
       <c r="F47" s="3">
-        <v>8900</v>
+        <v>12000</v>
       </c>
       <c r="G47" s="3">
-        <v>9000</v>
+        <v>6000</v>
       </c>
       <c r="H47" s="3">
-        <v>9100</v>
+        <v>14700</v>
       </c>
       <c r="I47" s="3">
-        <v>9100</v>
+        <v>10000</v>
       </c>
       <c r="J47" s="3">
-        <v>10300</v>
+        <v>6000</v>
       </c>
       <c r="K47" s="3">
         <v>10300</v>
       </c>
       <c r="L47" s="3">
+        <v>10300</v>
+      </c>
+      <c r="M47" s="3">
         <v>107500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>109000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>109600</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>109300</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>109500</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>110800</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>111700</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>111600</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>112500</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>113200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>112700</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>112400</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>112200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>112000</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>110900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>110700</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>110100</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>107100</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>108900</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>108300</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>106500</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>106000</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>106200</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>2550600</v>
+      </c>
+      <c r="E48" s="3">
         <v>2494800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>2461000</v>
       </c>
-      <c r="F48" s="3">
-        <v>2449000</v>
-      </c>
       <c r="G48" s="3">
+        <v>2478400</v>
+      </c>
+      <c r="H48" s="3">
         <v>2429200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>2390100</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>2330500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>2234100</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>2175600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>2101100</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1983800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>2019400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>1905700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>1831200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>1772700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>1760200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>1782200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>1793300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>1806900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>1862100</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>1888600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>1899900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>1926300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>1927100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>1955800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>1986300</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>2019400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>2037600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>2058400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>1042800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>1047800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>1055200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>1065500</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>834700</v>
+      </c>
+      <c r="E49" s="3">
         <v>835700</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>839700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>843800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>849200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>855000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>977100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>983200</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>990900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>998600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1006400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1097700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1108200</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1139600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1149400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1159200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1171900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1184600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1197200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1209900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1226300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1243000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1259100</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1275700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1292900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1310200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1325500</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1344800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1360800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>784100</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>785400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>788500</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>795800</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4622,8 +4736,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4723,109 +4840,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>77800</v>
+        <v>74900</v>
       </c>
       <c r="E52" s="3">
-        <v>79400</v>
+        <v>75600</v>
       </c>
       <c r="F52" s="3">
-        <v>70600</v>
+        <v>76000</v>
       </c>
       <c r="G52" s="3">
-        <v>76200</v>
+        <v>44000</v>
       </c>
       <c r="H52" s="3">
-        <v>65900</v>
+        <v>70500</v>
       </c>
       <c r="I52" s="3">
-        <v>63500</v>
+        <v>65000</v>
       </c>
       <c r="J52" s="3">
+        <v>66600</v>
+      </c>
+      <c r="K52" s="3">
         <v>61300</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>57600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>62300</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>59300</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>58100</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>134600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>135700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>140500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>135600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>51700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>49300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>51900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>28700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>30600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>30100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>30700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>23400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>36700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>30600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>28000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>14200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>10900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>9600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>9500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>9700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4925,109 +5048,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>3717700</v>
+      </c>
+      <c r="E54" s="3">
         <v>3610300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>3642200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>3628400</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>3686000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>3759400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>3891900</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>3887100</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>3969000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>3585700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>3595400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>3712700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>3729000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>3686800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>3673800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>3507300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>3383800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>3347600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>3355100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>3390300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>3443300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>3485700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>3524000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>3535300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>3596000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>3646800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>3708900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>3719100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>3761200</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>2061100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>2078200</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>2092800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>2104200</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5063,8 +5192,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5100,109 +5230,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>69300</v>
+      </c>
+      <c r="E57" s="3">
         <v>39800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>20500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>60100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>44400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50300</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>33100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>30400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>58800</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>39800</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>41000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>47900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>43500</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>27200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>25300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>22400</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>16700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>19900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>30900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>32200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>44700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>26000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>15700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>23100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>21000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>24100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>14200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>10100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>6400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>6800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>15000</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5210,504 +5344,519 @@
         <v>20600</v>
       </c>
       <c r="E58" s="3">
+        <v>20600</v>
+      </c>
+      <c r="F58" s="3">
         <v>19200</v>
       </c>
-      <c r="F58" s="3">
-        <v>18400</v>
-      </c>
       <c r="G58" s="3">
+        <v>26700</v>
+      </c>
+      <c r="H58" s="3">
         <v>15500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>16800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>16400</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>12800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>10300</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>9500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>8400</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>8000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>6900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>6500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>5000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>17600</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>23800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>24900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>25700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>27300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>27900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>29000</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>29300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>30500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>31800</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>32600</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>31600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>29700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>28800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>17800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>15800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>14900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>14400</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>208400</v>
+        <v>47800</v>
       </c>
       <c r="E59" s="3">
-        <v>232700</v>
+        <v>48500</v>
       </c>
       <c r="F59" s="3">
-        <v>238700</v>
+        <v>51700</v>
       </c>
       <c r="G59" s="3">
-        <v>258200</v>
+        <v>47900</v>
       </c>
       <c r="H59" s="3">
-        <v>248900</v>
+        <v>47700</v>
       </c>
       <c r="I59" s="3">
-        <v>248400</v>
+        <v>48900</v>
       </c>
       <c r="J59" s="3">
+        <v>49000</v>
+      </c>
+      <c r="K59" s="3">
         <v>221000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>262800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>228200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>254200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>236600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>266200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>225500</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>242500</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>227600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>216900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>183200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>192100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>186100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>198300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>190400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>229700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>220600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>231000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>213300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>221000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>202100</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>209900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>136800</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>138100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>128400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>122200</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>331400</v>
+      </c>
+      <c r="E60" s="3">
         <v>268800</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>272400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>317200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>318100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>316000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>318700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>266900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>303500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>296500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>302400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>285500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>321100</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>275400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>274700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>270500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>263100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>224800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>237700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>244300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>258400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>264100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>285000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>283600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>278500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>268900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>273600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>255900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>252900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>164700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>160400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>150100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>151600</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2386600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2268700</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2234700</v>
       </c>
-      <c r="F61" s="3">
-        <v>2134900</v>
-      </c>
       <c r="G61" s="3">
+        <v>2160900</v>
+      </c>
+      <c r="H61" s="3">
         <v>2129100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2135300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2136800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2129500</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2126000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2124000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2120900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2118900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2115300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2113300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2105800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1932700</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2193800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2198000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2209700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2250700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2285200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2309100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2308100</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2303600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>2302800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>2308800</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>2317400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>2311500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2311200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1376200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1375300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1376800</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1377500</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>374800</v>
+        <v>48800</v>
       </c>
       <c r="E62" s="3">
-        <v>383800</v>
+        <v>49400</v>
       </c>
       <c r="F62" s="3">
-        <v>396900</v>
+        <v>46300</v>
       </c>
       <c r="G62" s="3">
-        <v>393400</v>
+        <v>22600</v>
       </c>
       <c r="H62" s="3">
-        <v>408800</v>
+        <v>46000</v>
       </c>
       <c r="I62" s="3">
-        <v>431200</v>
+        <v>46200</v>
       </c>
       <c r="J62" s="3">
+        <v>48100</v>
+      </c>
+      <c r="K62" s="3">
         <v>445300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>506700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>430900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>443300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>471900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>891000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1014600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>960800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>914900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>535300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>552700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>554100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>548100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>540000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>553300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>554800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>532400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>526200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>554900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>573800</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>577700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>695400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>386900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>385800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>389700</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>363500</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5807,8 +5956,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5908,8 +6060,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6009,109 +6164,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>2920600</v>
+        <v>3074300</v>
       </c>
       <c r="E66" s="3">
-        <v>2899100</v>
+        <v>2912300</v>
       </c>
       <c r="F66" s="3">
-        <v>2857200</v>
+        <v>2890900</v>
       </c>
       <c r="G66" s="3">
-        <v>2848700</v>
+        <v>2849100</v>
       </c>
       <c r="H66" s="3">
-        <v>2868100</v>
+        <v>2840600</v>
       </c>
       <c r="I66" s="3">
-        <v>2894500</v>
+        <v>2860200</v>
       </c>
       <c r="J66" s="3">
+        <v>2886700</v>
+      </c>
+      <c r="K66" s="3">
         <v>2849300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>2943700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>2858800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>2873800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>2883400</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>3334500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>3410300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>3348000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>3124800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>2998900</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>2982000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>3007900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>3049400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>3089800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>3132600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>3153900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>3125500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>3113400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>3138300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>3170500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3150800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3265000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>1933300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>1926800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>1921800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>1897900</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6147,8 +6308,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6248,8 +6410,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6349,47 +6514,50 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
+        <v>408300</v>
+      </c>
+      <c r="E70" s="3">
         <v>396000</v>
       </c>
-      <c r="E70" s="3">
+      <c r="F70" s="3">
         <v>384300</v>
       </c>
-      <c r="F70" s="3">
+      <c r="G70" s="3">
         <v>372600</v>
       </c>
-      <c r="G70" s="3">
+      <c r="H70" s="3">
         <v>361300</v>
       </c>
-      <c r="H70" s="3">
+      <c r="I70" s="3">
         <v>350000</v>
       </c>
-      <c r="I70" s="3">
+      <c r="J70" s="3">
         <v>339300</v>
       </c>
-      <c r="J70" s="3">
+      <c r="K70" s="3">
         <v>328700</v>
       </c>
-      <c r="K70" s="3">
+      <c r="L70" s="3">
         <v>318300</v>
       </c>
-      <c r="L70" s="3">
+      <c r="M70" s="3">
         <v>308000</v>
       </c>
-      <c r="M70" s="3">
+      <c r="N70" s="3">
         <v>298200</v>
       </c>
-      <c r="N70" s="3">
+      <c r="O70" s="3">
         <v>288600</v>
       </c>
-      <c r="O70" s="3">
-        <v>0</v>
-      </c>
       <c r="P70" s="3">
         <v>0</v>
       </c>
@@ -6450,8 +6618,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6551,109 +6722,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>-401900</v>
+      </c>
+      <c r="E72" s="3">
         <v>-352800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>-297900</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>-262400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>-215100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>-157200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>-49000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>-11900</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>23300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>-259000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>-257300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>-141600</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>-156700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>-152000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>-96600</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>-34500</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>-27600</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>-42100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>-55800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>-71200</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>-65200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>-65500</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>-58100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>-50800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>-21900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>-11300</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF72" s="3">
         <v>-34900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>-6400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH72" s="3">
-        <v>0</v>
-      </c>
       <c r="AI72" s="3">
         <v>0</v>
       </c>
+      <c r="AJ72" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6753,8 +6930,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6854,8 +7034,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6955,109 +7138,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>226600</v>
+      </c>
+      <c r="E76" s="3">
         <v>293700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>358900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>398700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>476000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>541300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>658200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>709100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>707000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>418900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>423500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>540700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>394400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>276500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>325800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>382500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>385000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>365700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>347200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>340900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>353500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>353100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>370200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>409700</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>482600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>508500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>538300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>568300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>496200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>127800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>151500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>171000</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>206300</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7157,215 +7346,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44834</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44742</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44651</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44469</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44377</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44286</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44104</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44012</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43921</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43738</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42916</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42825</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>-66700</v>
+        <v>-49100</v>
       </c>
       <c r="E81" s="3">
-        <v>-47200</v>
+        <v>-55000</v>
       </c>
       <c r="F81" s="3">
-        <v>-58600</v>
+        <v>-35500</v>
       </c>
       <c r="G81" s="3">
-        <v>-69200</v>
+        <v>-47300</v>
       </c>
       <c r="H81" s="3">
-        <v>-119000</v>
+        <v>-57900</v>
       </c>
       <c r="I81" s="3">
-        <v>-47700</v>
+        <v>-108300</v>
       </c>
       <c r="J81" s="3">
+        <v>-37100</v>
+      </c>
+      <c r="K81" s="3">
         <v>-45500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>282300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-11500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-125300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>12400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-4700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-117500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-62100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-8800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>14100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>13500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>15300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-6000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>-7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-7700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-14100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-10700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-11500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>99700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-28600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-2800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>-3700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>6900</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7401,68 +7599,69 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>79800</v>
+        <v>79600</v>
       </c>
       <c r="E83" s="3">
-        <v>80600</v>
+        <v>79500</v>
       </c>
       <c r="F83" s="3">
-        <v>78300</v>
+        <v>77700</v>
       </c>
       <c r="G83" s="3">
+        <v>48700</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3">
+        <v>72500</v>
+      </c>
+      <c r="J83" s="3">
+        <v>72400</v>
+      </c>
+      <c r="K83" s="3">
         <v>79600</v>
       </c>
-      <c r="H83" s="3">
-        <v>79500</v>
-      </c>
-      <c r="I83" s="3">
-        <v>77700</v>
-      </c>
-      <c r="J83" s="3">
-        <v>79600</v>
-      </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>75700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>72500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>72400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>75100</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>73800</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>151700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>75600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>80800</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>80200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>81100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>82700</v>
       </c>
-      <c r="V83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="W83" s="3" t="s">
         <v>8</v>
       </c>
@@ -7478,8 +7677,8 @@
       <c r="AA83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB83" s="3">
-        <v>0</v>
+      <c r="AB83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC83" s="3">
         <v>0</v>
@@ -7502,8 +7701,11 @@
       <c r="AI83" s="3">
         <v>0</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7603,8 +7805,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7704,8 +7909,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7805,8 +8013,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7906,8 +8117,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8007,109 +8221,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>38600</v>
+      </c>
+      <c r="E89" s="3">
         <v>-8200</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>12000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>35300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>12200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>55100</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>5600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>76600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>59900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>81600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>22900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>110100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>185800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>98500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>67600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>115600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>96700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>85000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>90500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>85400</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>88300</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>75000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>93300</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>69700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>103500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>90800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>84800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>31700</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>41800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>51700</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>44600</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>58100</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8145,109 +8365,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-106700</v>
+      </c>
+      <c r="E91" s="3">
         <v>-85500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-98000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-90800</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-143300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-150000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-130800</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-123000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-164000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-176400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-156500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-140900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-144300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-195200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-76000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-65300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-56000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-53800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-42400</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-47900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-64600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-66400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-53400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-58100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-64000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-60800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-61900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-61200</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-29000</v>
       </c>
       <c r="AG91" s="3">
         <v>-29000</v>
       </c>
       <c r="AH91" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-31000</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-31900</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8347,8 +8571,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8448,109 +8675,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-106600</v>
+      </c>
+      <c r="E94" s="3">
         <v>-17900</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-97200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-91000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-144000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-53500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-128900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-135300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>370000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-113900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-104600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-93300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-209300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-283900</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-74700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-65300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-55100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-50000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-39800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-47700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-64400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-53500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-52200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-57600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-40700</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-62700</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-60400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-61300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-923400</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-29000</v>
       </c>
       <c r="AG94" s="3">
         <v>-29000</v>
       </c>
       <c r="AH94" s="3">
+        <v>-29000</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-21700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-24400</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8586,31 +8819,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8652,10 +8886,10 @@
         <v>0</v>
       </c>
       <c r="X96" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="3">
         <v>-27900</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-27600</v>
       </c>
       <c r="Z96" s="3">
         <v>-27600</v>
@@ -8667,7 +8901,7 @@
         <v>-27600</v>
       </c>
       <c r="AC96" s="3">
-        <v>-27400</v>
+        <v>-27600</v>
       </c>
       <c r="AD96" s="3">
         <v>-27400</v>
@@ -8676,10 +8910,10 @@
         <v>-27400</v>
       </c>
       <c r="AF96" s="3">
+        <v>-27400</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-19700</v>
-      </c>
-      <c r="AG96" s="3">
-        <v>-19600</v>
       </c>
       <c r="AH96" s="3">
         <v>-19600</v>
@@ -8687,8 +8921,11 @@
       <c r="AI96" s="3">
         <v>-19600</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>-19600</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8788,8 +9025,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8889,8 +9129,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8990,132 +9233,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E100" s="3">
         <v>24100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>94200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-5900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-4200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-4000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-4200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-6500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>71400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>141800</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>145800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>53500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-6700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-15000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-43500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-36500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-25200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-31100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-25700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-29900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-35800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-41300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-34900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-31100</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>899200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-23600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-23200</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-29300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-24800</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9192,105 +9441,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>39100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>2600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-84900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-113000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-45300</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-78000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-136200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>444000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-56200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-25500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-100600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>169600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>55800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>53800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>31700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>6200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-4300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>5800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-6800</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-7700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>7500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-10800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-6300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>8800</v>
       </c>
     </row>
